--- a/Бюджет/Бюджет по разделам РД — Берта Ромарио.xlsx
+++ b/Бюджет/Бюджет по разделам РД — Берта Ромарио.xlsx
@@ -504,11 +504,11 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>'ОВК'!F59/1000</f>
+        <f>'ОВК'!F68/1000</f>
         <v/>
       </c>
       <c r="C2" s="4">
-        <f>'ОВК'!G59/1000</f>
+        <f>'ОВК'!G68/1000</f>
         <v/>
       </c>
       <c r="D2" s="4">
@@ -529,11 +529,11 @@
         </is>
       </c>
       <c r="B3" s="4">
-        <f>'ОВ'!F47/1000</f>
+        <f>'ОВ'!F36/1000</f>
         <v/>
       </c>
       <c r="C3" s="4">
-        <f>'ОВ'!G47/1000</f>
+        <f>'ОВ'!G36/1000</f>
         <v/>
       </c>
       <c r="D3" s="4">
@@ -541,10 +541,10 @@
         <v/>
       </c>
       <c r="E3" s="4" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -554,11 +554,11 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>'ВК'!F35/1000</f>
+        <f>'ВК'!F37/1000</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>'ВК'!G35/1000</f>
+        <f>'ВК'!G37/1000</f>
         <v/>
       </c>
       <c r="D4" s="4">
@@ -579,11 +579,11 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>'ЭОМ'!F26/1000</f>
+        <f>'ЭОМ'!F36/1000</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>'ЭОМ'!G26/1000</f>
+        <f>'ЭОМ'!G36/1000</f>
         <v/>
       </c>
       <c r="D5" s="4">
@@ -604,11 +604,11 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>'СС'!F24/1000</f>
+        <f>'СС'!F29/1000</f>
         <v/>
       </c>
       <c r="C6" s="4">
-        <f>'СС'!G24/1000</f>
+        <f>'СС'!G29/1000</f>
         <v/>
       </c>
       <c r="D6" s="4">
@@ -629,11 +629,11 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>'МЗ-ПС'!F25/1000</f>
+        <f>'МЗ-ПС'!F27/1000</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>'МЗ-ПС'!G25/1000</f>
+        <f>'МЗ-ПС'!G27/1000</f>
         <v/>
       </c>
       <c r="D7" s="4">
@@ -641,10 +641,10 @@
         <v/>
       </c>
       <c r="E7" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8">
@@ -712,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -770,7 +770,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Приточно-вытяжная установка с роторным рекуператором (η≥75%), L=1050 м³/ч, Pсв=250 Па, EC-вентиляторы, электронагреватель 3.5 кВт / 380 В, фильтры приток ePM1 55% (F7), вытяжка ePM10 50% (M5), автоматика с пультом и датчиком CO₂</t>
+          <t>Приточно-вытяжная установка с роторным рекуператором (η≥80 %), L=1050/1050 м³/ч, Pсв=250 Па, EC-вентиляторы, водяной калорифер 7 кВт (гликоль 30 %, узел обвязки с насосом и 3-ходовым клапаном), фильтры приток ePM1 55 % (F7), вытяжка ePM10 50 % (M5), автоматика с Modbus TCP/RTU, датчиками CO₂/RH и защитой калорифера от замерзания</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Диффузор потолочный/стеновой с пленумом под 2…4 воздуховода Ø90</t>
+          <t>Диффузор щелевой линейный 1–2 щели, L=1000 мм, с камерой статического давления и регулятором</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="F9" s="4">
         <f>C9*D9</f>
@@ -1010,7 +1010,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Распределительный коллектор (камера статического давления) Ø200/Ø160, 6…14 выходов Ø90, со звукопоглощением и ревизией</t>
+          <t>Решётка/клапан вытяжной потолочный с регулятором Ø100…Ø160</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>45000</v>
+        <v>4000</v>
       </c>
       <c r="F10" s="4">
         <f>C10*D10</f>
@@ -1040,22 +1040,22 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Воздуховод полимерный гибкий двухслойный Ø90 с антистатическим и антибактериальным покрытием</t>
+          <t>Дроссель-клапан Ø125…Ø315 с ручным приводом</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>420</v>
+        <v>18</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="F11" s="4">
         <f>C11*D11</f>
@@ -1070,22 +1070,22 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Дроссель-клапан Ø125…Ø315 с ручным приводом</t>
+          <t>Воздуховоды из оцинкованной стали круглые спирально-навивные, δ=0,5 мм, Ø100…Ø315 (ГОСТ 14918-2020)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F12" s="4">
         <f>C12*D12</f>
@@ -1100,7 +1100,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Воздуховоды из оцинкованной стали круглые спирально-навивные, δ=0,5 мм, Ø125…Ø315 (ГОСТ 14918-2020)</t>
+          <t>Фасонные изделия к воздуховодам п.10</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F13" s="4">
         <f>C13*D13</f>
@@ -1130,7 +1130,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Фасонные изделия к воздуховодам п.11</t>
+          <t>Изоляция теплоизоляционная из вспененного каучука δ=19 мм, самоклеящаяся</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="F14" s="4">
         <f>C14*D14</f>
@@ -1160,7 +1160,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Изоляция теплоизоляционная из вспененного каучука δ=19 мм, самоклеящаяся</t>
+          <t>Изоляция из вспененного каучука δ=32 мм, с покрытием (паронепроницаемая)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="F15" s="4">
         <f>C15*D15</f>
@@ -1190,22 +1190,22 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Изоляция из вспененного каучука δ=32 мм, с покрытием (паронепроницаемая)</t>
+          <t>Шланг дренажный ПВХ Ø20 с сифоном (гидрозатвор)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>3000</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>4500</v>
       </c>
       <c r="F16" s="4">
         <f>C16*D16</f>
@@ -1220,22 +1220,22 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Шланг дренажный ПВХ Ø20 с сифоном (гидрозатвор)</t>
+          <t>Датчик CO₂ + RH канальный/комнатный, выход 0–10 В или Modbus</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1500</v>
+        <v>8000</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3000</v>
+        <v>25000</v>
       </c>
       <c r="F17" s="4">
         <f>C17*D17</f>
@@ -1250,22 +1250,22 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Приточная установка компактная, L=400 м³/ч, Pсв=200 Па, электронагреватель 6 кВт / 380 В, фильтр G4, клапан с эл. приводом, автоматика с блокировкой от зонта</t>
+          <t>Датчик перепада давления «помещение — улица» (дифманометр) с выходом в HA</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>120000</v>
+        <v>15000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>220000</v>
+        <v>40000</v>
       </c>
       <c r="F18" s="4">
         <f>C18*D18</f>
@@ -1280,22 +1280,22 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Вытяжной зонт кухонный с вентилятором, L=450 м³/ч</t>
+          <t>Пароувлажнитель канальный, 1.5 кг/ч, 1.12 кВт, с паровой форсункой и гигростатом</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="F19" s="4">
         <f>C19*D19</f>
@@ -1305,31 +1305,27 @@
         <f>C19*E19</f>
         <v/>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>поставка заказчика</t>
-        </is>
-      </c>
+      <c r="H19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Клапан обратный Ø200</t>
+          <t>Пароувлажнитель канальный, 1.5 кг/ч, 1.12 кВт, с паровой форсункой и гигростатом</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1500</v>
+        <v>120000</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3000</v>
+        <v>250000</v>
       </c>
       <c r="F20" s="4">
         <f>C20*D20</f>
@@ -1344,22 +1340,22 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Воздуховоды из оцинкованной стали Ø200, δ=0,5 мм</t>
+          <t>Пароувлажнитель канальный, 1.5 кг/ч, 1.12 кВт, с паровой форсункой и гигростатом</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1200</v>
+        <v>120000</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2000</v>
+        <v>250000</v>
       </c>
       <c r="F21" s="4">
         <f>C21*D21</f>
@@ -1374,22 +1370,22 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Изоляция вспененный каучук δ=32 мм с покрытием</t>
+          <t>Пароувлажнитель канальный, 1.5 кг/ч, 1.12 кВт, с паровой форсункой и гигростатом</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3000</v>
+        <v>120000</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4500</v>
+        <v>250000</v>
       </c>
       <c r="F22" s="4">
         <f>C22*D22</f>
@@ -1404,7 +1400,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Узел прохода через кровлю Ø200 с зонтом</t>
+          <t>Пароувлажнитель канальный, 1.5 кг/ч, 1.12 кВт, с паровой форсункой и гигростатом</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1416,10 +1412,10 @@
         <v>1</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>15000</v>
+        <v>120000</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>30000</v>
+        <v>250000</v>
       </c>
       <c r="F23" s="4">
         <f>C23*D23</f>
@@ -1434,22 +1430,22 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Решётка наружная Ø200 с сеткой</t>
+          <t>Пароувлажнитель канальный, 3.0 кг/ч, 2.25 кВт, с паровой форсункой и гигростатом</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2000</v>
+        <v>180000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4000</v>
+        <v>350000</v>
       </c>
       <c r="F24" s="4">
         <f>C24*D24</f>
@@ -1464,22 +1460,22 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Решётка/диффузор приточный 400×150 с регулятором</t>
+          <t>Установка обратного осмоса 50–100 л/ч с баком 50 л (подпитка ПУ)</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3000</v>
+        <v>60000</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6000</v>
+        <v>150000</v>
       </c>
       <c r="F25" s="4">
         <f>C25*D25</f>
@@ -1494,22 +1490,22 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Вентилятор канальный термостойкий (до +120 °C), L=130 м³/ч, Pсв=150 Па, Ø125</t>
+          <t>Трубопровод подпитки PE-X Ø16 и дренаж ПУ</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>25000</v>
+        <v>150</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>50000</v>
+        <v>300</v>
       </c>
       <c r="F26" s="4">
         <f>C26*D26</f>
@@ -1524,22 +1520,22 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Клапан вытяжной для сауны регулируемый (дерево/нерж.) Ø125</t>
+          <t>Приточная установка компактная, L=400 м³/ч, Pсв=200 Па, водяной калорифер 5.5 кВт (гликоль 30 %), фильтр G4, утеплённый клапан с эл. приводом, шумоглушитель Ø200, автоматика с блокировкой от зонта</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3000</v>
+        <v>120000</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6000</v>
+        <v>220000</v>
       </c>
       <c r="F27" s="4">
         <f>C27*D27</f>
@@ -1554,7 +1550,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Клапан обратный Ø125</t>
+          <t>Вытяжной зонт кухонный с вентилятором, L=450 м³/ч, сухой контакт «вкл»</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1566,10 +1562,10 @@
         <v>1</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F28" s="4">
         <f>C28*D28</f>
@@ -1579,21 +1575,25 @@
         <f>C28*E28</f>
         <v/>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>поставка заказчика</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Воздуховод из нержавеющей стали Ø125, δ=0,5 мм</t>
+          <t>Клапан обратный Ø200 + клапан утеплённый Ø200 с эл. приводом</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D29" s="4" t="n">
         <v>1500</v>
@@ -1614,7 +1614,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Изоляция базальтовая фольгированная δ=30 мм</t>
+          <t>Воздуховоды из оцинкованной стали Ø200, δ=0,5 мм</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F30" s="4">
         <f>C30*D30</f>
@@ -1644,22 +1644,22 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Узел прохода через кровлю Ø125 с зонтом</t>
+          <t>Изоляция вспененный каучук δ=32 мм с покрытием</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>25000</v>
+        <v>4500</v>
       </c>
       <c r="F31" s="4">
         <f>C31*D31</f>
@@ -1674,7 +1674,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Канал вытяжной естественный Ø200 оцинк. с утеплением δ=50 мм, с дефлектором над кровлей</t>
+          <t>Узел прохода через кровлю Ø200 с зонтом</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="F32" s="4">
         <f>C32*D32</f>
@@ -1704,7 +1704,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Решётка вентиляционная наружная 300×200 с утеплённой заслонкой</t>
+          <t>Решётка/диффузор приточный 400×150 с регулятором</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1716,10 +1716,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="F33" s="4">
         <f>C33*D33</f>
@@ -1734,22 +1734,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Воздуховод подачи воздуха на горение к топке камина Ø125 с заслонкой и наружной решёткой</t>
+          <t>Вентилятор канальный термостойкий (до +120 °C), L=130 м³/ч, Pсв=150 Па, Ø125</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="F34" s="4">
         <f>C34*D34</f>
@@ -1764,7 +1764,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Наружный блок мини-VRF (тепловой насос), Qх=22.4 кВт, R410A/R32, 380 В</t>
+          <t>Клапан вытяжной для сауны регулируемый (дерево/нерж.) Ø125</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1776,10 +1776,10 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>450000</v>
+        <v>3000</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>800000</v>
+        <v>6000</v>
       </c>
       <c r="F35" s="4">
         <f>C35*D35</f>
@@ -1794,7 +1794,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Наружный блок мини-VRF (тепловой насос), Qх=12.1 кВт, R410A/R32, 380 В</t>
+          <t>Клапан обратный Ø125</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>280000</v>
+        <v>1000</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>480000</v>
+        <v>2000</v>
       </c>
       <c r="F36" s="4">
         <f>C36*D36</f>
@@ -1824,22 +1824,22 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.2 кВт</t>
+          <t>Воздуховод из нержавеющей стали Ø125, δ=0,5 мм</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>53200</v>
+        <v>1500</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>87600</v>
+        <v>3000</v>
       </c>
       <c r="F37" s="4">
         <f>C37*D37</f>
@@ -1854,22 +1854,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=4.5 кВт</t>
+          <t>Изоляция базальтовая фольгированная δ=30 мм</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>67000</v>
+        <v>600</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>106000</v>
+        <v>1000</v>
       </c>
       <c r="F38" s="4">
         <f>C38*D38</f>
@@ -1884,22 +1884,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=7.1 кВт</t>
+          <t>Узел прохода через кровлю Ø125 с зонтом</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>82600</v>
+        <v>12000</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>126800</v>
+        <v>25000</v>
       </c>
       <c r="F39" s="4">
         <f>C39*D39</f>
@@ -1914,7 +1914,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=5.6 кВт</t>
+          <t>Гигростат / датчик RH термостойкий для управления В2</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1926,10 +1926,10 @@
         <v>1</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>73600</v>
+        <v>8000</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>114800</v>
+        <v>20000</v>
       </c>
       <c r="F40" s="4">
         <f>C40*D40</f>
@@ -1944,22 +1944,22 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.8 кВт</t>
+          <t>Канал вытяжной естественный Ø200 оцинк. с утеплением δ=50 мм, с дефлектором над кровлей</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>56800</v>
+        <v>40000</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>92400</v>
+        <v>80000</v>
       </c>
       <c r="F41" s="4">
         <f>C41*D41</f>
@@ -1974,7 +1974,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.8 кВт</t>
+          <t>Решётка вентиляционная наружная 300×200 с утеплённой заслонкой и подогревом 300 Вт, воздуховод Ø160 через стену</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1986,10 +1986,10 @@
         <v>1</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>56800</v>
+        <v>8000</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>92400</v>
+        <v>15000</v>
       </c>
       <c r="F42" s="4">
         <f>C42*D42</f>
@@ -2004,22 +2004,22 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.8 кВт</t>
+          <t>Решётка 300×150 в наружной стене по оси 7 на уровне пола, с утеплённой заслонкой — воздух на горение камина</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>56800</v>
+        <v>10000</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>92400</v>
+        <v>25000</v>
       </c>
       <c r="F43" s="4">
         <f>C43*D43</f>
@@ -2034,7 +2034,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.2 кВт</t>
+          <t>Наружный блок мульти-сплит / мини-VRF (тепловой насос), Qх=20.0 кВт, R32 или R410A, 380 В, шлюз Modbus</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2046,10 +2046,10 @@
         <v>1</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>53200</v>
+        <v>600000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>87600</v>
+        <v>1000000</v>
       </c>
       <c r="F44" s="4">
         <f>C44*D44</f>
@@ -2064,7 +2064,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.2 кВт</t>
+          <t>Наружный блок мульти-сплит / мини-VRF (тепловой насос), Qх=14.0 кВт, R32 или R410A, 380 В, шлюз Modbus</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2076,10 +2076,10 @@
         <v>1</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>53200</v>
+        <v>420000</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>87600</v>
+        <v>750000</v>
       </c>
       <c r="F45" s="4">
         <f>C45*D45</f>
@@ -2094,7 +2094,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.2 кВт</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2106,10 +2106,10 @@
         <v>1</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>53200</v>
+        <v>77600</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>87600</v>
+        <v>126400</v>
       </c>
       <c r="F46" s="4">
         <f>C46*D46</f>
@@ -2124,7 +2124,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.8 кВт</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=3.6 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2136,10 +2136,10 @@
         <v>1</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>56800</v>
+        <v>88800</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>92400</v>
+        <v>143200</v>
       </c>
       <c r="F47" s="4">
         <f>C47*D47</f>
@@ -2154,7 +2154,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Разветвитель (рефнет) фреоновый</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=5.6 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2163,13 +2163,13 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>4000</v>
+        <v>104800</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>8000</v>
+        <v>167200</v>
       </c>
       <c r="F48" s="4">
         <f>C48*D48</f>
@@ -2184,22 +2184,22 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая Ø6,35…Ø19,05 (ГОСТ Р 52318-2005)</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=5.6 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>900</v>
+        <v>104800</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1500</v>
+        <v>167200</v>
       </c>
       <c r="F49" s="4">
         <f>C49*D49</f>
@@ -2214,22 +2214,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Изоляция трубная вспененный каучук δ=13 мм</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.8 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>120</v>
+        <v>82400</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>250</v>
+        <v>133600</v>
       </c>
       <c r="F50" s="4">
         <f>C50*D50</f>
@@ -2244,22 +2244,22 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Кабель межблочной связи экранированный 2×0,75</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.8 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>60</v>
+        <v>82400</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>120</v>
+        <v>133600</v>
       </c>
       <c r="F51" s="4">
         <f>C51*D51</f>
@@ -2274,22 +2274,22 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Дренажная труба ПП Ø32 с гидрозатвором (сухой затвор)</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>250</v>
+        <v>77600</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>500</v>
+        <v>126400</v>
       </c>
       <c r="F52" s="4">
         <f>C52*D52</f>
@@ -2304,22 +2304,22 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Опора наружного блока (рама на фундаментных блоках)</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>15000</v>
+        <v>77600</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>30000</v>
+        <v>126400</v>
       </c>
       <c r="F53" s="4">
         <f>C53*D53</f>
@@ -2334,7 +2334,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Пульт управления проводной индивидуальный</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2343,13 +2343,13 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>6000</v>
+        <v>77600</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>12000</v>
+        <v>126400</v>
       </c>
       <c r="F54" s="4">
         <f>C54*D54</f>
@@ -2364,108 +2364,378 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Материалы и оборудование (этап 1)</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>77600</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>126400</v>
+      </c>
       <c r="F55" s="4">
-        <f>SUMIF(H2:H54,"",F2:F54)</f>
+        <f>C55*D55</f>
         <v/>
       </c>
       <c r="G55" s="4">
-        <f>SUMIF(H2:H54,"",G2:G54)</f>
-        <v/>
-      </c>
-      <c r="H55" s="3" t="n"/>
+        <f>C55*E55</f>
+        <v/>
+      </c>
+      <c r="H55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Монтажные работы</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n">
-        <v>1190070</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>1700100</v>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>77600</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>126400</v>
+      </c>
+      <c r="F56" s="4">
+        <f>C56*D56</f>
+        <v/>
+      </c>
+      <c r="G56" s="4">
+        <f>C56*E56</f>
+        <v/>
+      </c>
+      <c r="H56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Крепёж, расходники, доставка</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="n">
-        <v>170010</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>272016</v>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
+          <t>Разветвитель (рефнет) фреоновый</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F57" s="4">
+        <f>C57*D57</f>
+        <v/>
+      </c>
+      <c r="G57" s="4">
+        <f>C57*E57</f>
+        <v/>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
+          <t>Труба медная отожжённая Ø6,35…Ø19,05 (ГОСТ Р 52318-2005)</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F58" s="4">
+        <f>C58*D58</f>
+        <v/>
+      </c>
+      <c r="G58" s="4">
+        <f>C58*E58</f>
+        <v/>
+      </c>
+      <c r="H58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Изоляция трубная вспененный каучук δ=13 мм</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="F59" s="4">
+        <f>C59*D59</f>
+        <v/>
+      </c>
+      <c r="G59" s="4">
+        <f>C59*E59</f>
+        <v/>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Кабель межблочной связи экранированный 2×0,75</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="F60" s="4">
+        <f>C60*D60</f>
+        <v/>
+      </c>
+      <c r="G60" s="4">
+        <f>C60*E60</f>
+        <v/>
+      </c>
+      <c r="H60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Дренажная труба ПП Ø32 с гидрозатвором (сухой затвор), дренажные помпы где нет уклона</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F61" s="4">
+        <f>C61*D61</f>
+        <v/>
+      </c>
+      <c r="G61" s="4">
+        <f>C61*E61</f>
+        <v/>
+      </c>
+      <c r="H61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Короб декоративный с жалюзи для НБ1, НБ2 на опорах h ≥ 400 мм</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F62" s="4">
+        <f>C62*D62</f>
+        <v/>
+      </c>
+      <c r="G62" s="4">
+        <f>C62*E62</f>
+        <v/>
+      </c>
+      <c r="H62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Шлюз Modbus/BACnet для внутренних блоков (интеграция в Home Assistant)</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F63" s="4">
+        <f>C63*D63</f>
+        <v/>
+      </c>
+      <c r="G63" s="4">
+        <f>C63*E63</f>
+        <v/>
+      </c>
+      <c r="H63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Материалы и оборудование (этап 1)</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4">
+        <f>SUMIF(H2:H63,"",F2:F63)</f>
+        <v/>
+      </c>
+      <c r="G64" s="4">
+        <f>SUMIF(H2:H63,"",G2:G63)</f>
+        <v/>
+      </c>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Монтажные работы</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="n">
+        <v>1648430</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>2354900</v>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Крепёж, расходники, доставка</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n">
+        <v>235490</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>376784</v>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
           <t>Пусконаладка: аэродинамические испытания, балансировка, пуск VRF</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n">
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n">
         <v>80000</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G67" s="4" t="n">
         <v>150000</v>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>оценка</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>ИТОГО этап 1</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6">
-        <f>SUM(F55:F58)</f>
-        <v/>
-      </c>
-      <c r="G59" s="6">
-        <f>SUM(G55:G58)</f>
-        <v/>
-      </c>
-      <c r="H59" s="5" t="n"/>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6">
+        <f>SUM(F64:F67)</f>
+        <v/>
+      </c>
+      <c r="G68" s="6">
+        <f>SUM(G64:G67)</f>
+        <v/>
+      </c>
+      <c r="H68" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2478,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -2536,7 +2806,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Котёл пеллетный 50 кВт с автоматическим розжигом, модуляцией, бункером 500 л, автоочисткой теплообменника</t>
+          <t>Котёл пеллетный 30 кВт (модуляция 9–30 кВт) с автоматическим розжигом, бункером 500–600 л, автоочисткой горелки и теплообменника, зольником от 20 л, Modbus/OpenTherm</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2548,10 +2818,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>700000</v>
+        <v>500000</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>2000000</v>
+        <v>1600000</v>
       </c>
       <c r="F2" s="4">
         <f>C2*D2</f>
@@ -2566,22 +2836,22 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Подача пеллет со склада (шнек/вакуум) с огнезащитной муфтой</t>
+          <t>Котёл электрический 12 кВт, 3 ступени по 4 кВт, 380 В</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>350000</v>
+        <v>90000</v>
       </c>
       <c r="F3" s="4">
         <f>C3*D3</f>
@@ -2596,22 +2866,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Котёл электрический 24 кВт, 380 В, 3 ступени</t>
+          <t>Место и подключения под газовый конденсационный котёл 35–45 кВт</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>110000</v>
+        <v>80000</v>
       </c>
       <c r="F4" s="4">
         <f>C4*D4</f>
@@ -2626,7 +2896,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Котёл газовый конденсационный 50 кВт с коаксиальным дымоходом</t>
+          <t>Буферная ёмкость 1000 л, 4 патрубка, изоляция 100 мм</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2638,10 +2908,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>550000</v>
+        <v>220000</v>
       </c>
       <c r="F5" s="4">
         <f>C5*D5</f>
@@ -2651,16 +2921,12 @@
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>этап 2</t>
-        </is>
-      </c>
+      <c r="H5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Буферная ёмкость 1000 л с теплоизоляцией</t>
+          <t>Бойлер косвенного нагрева 500 л, змеевик ≥ 2 м², ТЭН 6 кВт, Ø750, высота 1,8 м</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2672,10 +2938,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>120000</v>
+        <v>130000</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>220000</v>
+        <v>250000</v>
       </c>
       <c r="F6" s="4">
         <f>C6*D6</f>
@@ -2690,22 +2956,22 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Бойлер косвенного нагрева 300 л, змеевик ≥ 30 кВт</t>
+          <t>Термосмеситель ГВС 55 °C, насос рециркуляции Н5 с таймером</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>90000</v>
+        <v>25000</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>180000</v>
+        <v>60000</v>
       </c>
       <c r="F7" s="4">
         <f>C7*D7</f>
@@ -2750,7 +3016,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Насосные группы (прямая/смесительная), Ду25…32, насосы с ЭК</t>
+          <t>Насосные группы: ТП 40/32 (смесит.), приборы 70/50 (погодная), калориферы, загрузка бойлера; насосы с ЭК</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2759,7 +3025,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>35000</v>
@@ -2780,22 +3046,22 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Гидрострелка/распределительный коллектор на 5 контуров</t>
+          <t>Пластинчатый теплообменник калориферов П1/П2 ≈ 12 кВт + насос гликоля Н6, бак и ГБ гликолевого контура</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>80000</v>
+        <v>150000</v>
       </c>
       <c r="F10" s="4">
         <f>C10*D10</f>
@@ -2810,7 +3076,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Погодозависимый каскадный контроллер с GSM/Wi-Fi</t>
+          <t>Погодозависимый каскадный контроллер (Modbus/OpenTherm → Home Assistant), GSM</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2840,7 +3106,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Расширительные баки: отопление 50 л, ГВС 24 л</t>
+          <t>Расширительный бак отопления 150 л</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2849,13 +3115,13 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="F12" s="4">
         <f>C12*D12</f>
@@ -2870,22 +3136,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Группы безопасности котлов, клапан термозащиты К1</t>
+          <t>Расширительный бак ГВС 25 л</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="F13" s="4">
         <f>C13*D13</f>
@@ -2900,7 +3166,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Дымоход-сэндвич Ø150 нерж., по фасаду, с кронштейнами и разделкой</t>
+          <t>Группы безопасности 3 бар, клапан термической защиты К1, подпитка через разделитель</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2912,10 +3178,10 @@
         <v>1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>120000</v>
+        <v>5000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>220000</v>
+        <v>12000</v>
       </c>
       <c r="F14" s="4">
         <f>C14*D14</f>
@@ -2930,22 +3196,22 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Огнезащитная облицовка котельной (ЦСП, базальтовый картон, керамогранит)</t>
+          <t>Дымоход-сэндвич Ø150/250 нерж. с конденсатоотводом, через КД4/КД5 в коробе 450×450, с проходными узлами</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3000</v>
+        <v>120000</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>6000</v>
+        <v>220000</v>
       </c>
       <c r="F15" s="4">
         <f>C15*D15</f>
@@ -2960,22 +3226,22 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Дверь противопожарная EI 30</t>
+          <t>Огнезащитная облицовка котельной (ЦСП, базальтовый картон, керамогранит)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>35000</v>
+        <v>3000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>70000</v>
+        <v>6000</v>
       </c>
       <c r="F16" s="4">
         <f>C16*D16</f>
@@ -3029,7 +3295,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3040</v>
+        <v>1330</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>110</v>
@@ -3050,7 +3316,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Коллекторный блок тёплого пола с расходомерами, сервоприводами 24 В, в шкафу</t>
+          <t>Коллекторный блок ТП с расходомерами и сервоприводами 24 В, в шкафу</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3059,13 +3325,13 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="F19" s="4">
         <f>C19*D19</f>
@@ -3080,7 +3346,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Демпферная лента, якорная скоба/маты, фибра</t>
+          <t>Демпферная лента, маты с бобышками / якорная скоба</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3089,7 +3355,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>360</v>
+        <v>160</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>400</v>
@@ -3110,22 +3376,22 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Комнатные термостаты (проводные/радио)</t>
+          <t>Контроллер сервоприводов (Zigbee / Modbus) + датчики Zigbee в помещениях</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4000</v>
+        <v>30000</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>12000</v>
+        <v>80000</v>
       </c>
       <c r="F21" s="4">
         <f>C21*D21</f>
@@ -3140,7 +3406,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный естественный, L=2000</t>
+          <t>Конвектор внутрипольный естественный, L≈2000, в приямке 90–110 мм</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3149,7 +3415,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>60000</v>
@@ -3170,7 +3436,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В, L=2000</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В, L≈2000, в приямке 90–110 мм</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3179,7 +3445,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>110000</v>
@@ -3200,7 +3466,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В, L=2000</t>
+          <t>Радиатор стальной панельный 22-500, 70/50 °C</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3212,10 +3478,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>110000</v>
+        <v>6000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>170000</v>
+        <v>12000</v>
       </c>
       <c r="F24" s="4">
         <f>C24*D24</f>
@@ -3230,7 +3496,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В, L=2000</t>
+          <t>Конвектор настенный низкий h = 200–350 мм, 600–1200 Вт, 70/50 °C</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3239,13 +3505,13 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>110000</v>
+        <v>25000</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>170000</v>
+        <v>60000</v>
       </c>
       <c r="F25" s="4">
         <f>C25*D25</f>
@@ -3260,7 +3526,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 22-500, Q≈430 Вт</t>
+          <t>Радиатор стальной панельный 22-500, 70/50 °C</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -3269,7 +3535,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>6000</v>
@@ -3290,22 +3556,22 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В, L=2000</t>
+          <t>Коллектор приборов 2 этажа с балансировочными клапанами, в шкафу</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>110000</v>
+        <v>30000</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>170000</v>
+        <v>70000</v>
       </c>
       <c r="F27" s="4">
         <f>C27*D27</f>
@@ -3320,7 +3586,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В, L=2000</t>
+          <t>Блок питания 24 В для вентиляторов конвекторов</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3329,13 +3595,13 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>110000</v>
+        <v>6000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>170000</v>
+        <v>12000</v>
       </c>
       <c r="F28" s="4">
         <f>C28*D28</f>
@@ -3350,22 +3616,22 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный естественный, L=2000</t>
+          <t>Труба PE-X / PE-RT Ø25–40 в изоляции 9 мм (магистрали, стояки)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>60000</v>
+        <v>450</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>95000</v>
+        <v>900</v>
       </c>
       <c r="F29" s="4">
         <f>C29*D29</f>
@@ -3380,22 +3646,22 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 22-500, Q≈570 Вт</t>
+          <t>Труба PE-X 16–20 в гофре (подводки к приборам 2 этажа, в стяжке ЦПС)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1</v>
+        <v>380</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6000</v>
+        <v>150</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>12000</v>
+        <v>300</v>
       </c>
       <c r="F30" s="4">
         <f>C30*D30</f>
@@ -3410,22 +3676,22 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 22-500, Q≈160 Вт</t>
+          <t>Нагревательный мат 150 Вт/м² в плиточном клее, датчик пола в гофре, терморегулятор Zigbee</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="F31" s="4">
         <f>C31*D31</f>
@@ -3440,438 +3706,108 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный естественный, L=2000</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>95000</v>
-      </c>
+          <t>Материалы и оборудование (этап 1)</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
       <c r="F32" s="4">
-        <f>C32*D32</f>
+        <f>SUMIF(H2:H31,"",F2:F31)</f>
         <v/>
       </c>
       <c r="G32" s="4">
-        <f>C32*E32</f>
-        <v/>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
+        <f>SUMIF(H2:H31,"",G2:G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Полотенцесушитель водяной 600 Вт</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F33" s="4">
-        <f>C33*D33</f>
-        <v/>
-      </c>
-      <c r="G33" s="4">
-        <f>C33*E33</f>
-        <v/>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
+          <t>Монтажные работы</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n">
+        <v>911940</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>1367910</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный естественный, L=2000</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>95000</v>
-      </c>
-      <c r="F34" s="4">
-        <f>C34*D34</f>
-        <v/>
-      </c>
-      <c r="G34" s="4">
-        <f>C34*E34</f>
-        <v/>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
+          <t>Крепёж, расходники, доставка</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n">
+        <v>151990</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>243184</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный естественный, L=2000</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="4" t="n">
+          <t>Пусконаладка котельной, гидравлическая балансировка тёплых полов</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n">
         <v>60000</v>
       </c>
-      <c r="E35" s="4" t="n">
-        <v>95000</v>
-      </c>
-      <c r="F35" s="4">
-        <f>C35*D35</f>
-        <v/>
-      </c>
-      <c r="G35" s="4">
-        <f>C35*E35</f>
-        <v/>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="G35" s="4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Полотенцесушитель водяной 600 Вт</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F36" s="4">
-        <f>C36*D36</f>
-        <v/>
-      </c>
-      <c r="G36" s="4">
-        <f>C36*E36</f>
-        <v/>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Конвектор внутрипольный естественный, L=2000</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>95000</v>
-      </c>
-      <c r="F37" s="4">
-        <f>C37*D37</f>
-        <v/>
-      </c>
-      <c r="G37" s="4">
-        <f>C37*E37</f>
-        <v/>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Конвектор внутрипольный естественный, L=2000</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>95000</v>
-      </c>
-      <c r="F38" s="4">
-        <f>C38*D38</f>
-        <v/>
-      </c>
-      <c r="G38" s="4">
-        <f>C38*E38</f>
-        <v/>
-      </c>
-      <c r="H38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Полотенцесушитель водяной 600 Вт</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F39" s="4">
-        <f>C39*D39</f>
-        <v/>
-      </c>
-      <c r="G39" s="4">
-        <f>C39*E39</f>
-        <v/>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Радиатор стальной панельный 22-500, Q≈410 Вт</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F40" s="4">
-        <f>C40*D40</f>
-        <v/>
-      </c>
-      <c r="G40" s="4">
-        <f>C40*E40</f>
-        <v/>
-      </c>
-      <c r="H40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Труба PE-Xa/PE-RT 25…40 мм в изоляции 9 мм (магистрали, стояки)</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>900</v>
-      </c>
-      <c r="F41" s="4">
-        <f>C41*D41</f>
-        <v/>
-      </c>
-      <c r="G41" s="4">
-        <f>C41*E41</f>
-        <v/>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Блок питания 24 В для вентиляторных конвекторов</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F42" s="4">
-        <f>C42*D42</f>
-        <v/>
-      </c>
-      <c r="G42" s="4">
-        <f>C42*E42</f>
-        <v/>
-      </c>
-      <c r="H42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Материалы и оборудование (этап 1)</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4">
-        <f>SUMIF(H2:H42,"",F2:F42)</f>
-        <v/>
-      </c>
-      <c r="G43" s="4">
-        <f>SUMIF(H2:H42,"",G2:G42)</f>
-        <v/>
-      </c>
-      <c r="H43" s="3" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Монтажные работы</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n">
-        <v>1260120</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>1890180</v>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Крепёж, расходники, доставка</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n">
-        <v>210020</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>336032</v>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Пусконаладка котельной, гидравлическая балансировка тёплых полов</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n">
-        <v>60000</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>150000</v>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>ИТОГО этап 1</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6">
-        <f>SUM(F43:F46)</f>
-        <v/>
-      </c>
-      <c r="G47" s="6">
-        <f>SUM(G43:G46)</f>
-        <v/>
-      </c>
-      <c r="H47" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6">
+        <f>SUM(F32:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="6">
+        <f>SUM(G32:G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3884,7 +3820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -3942,7 +3878,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду32, фильтр сетчатый Ду32, обратный клапан Ду32</t>
+          <t>Кран шаровой Ду32, фильтр сетчатый 100 мкм Ду32, обратный клапан Ду32</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3972,7 +3908,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Счётчик холодной воды Ду20…25 с импульсным выходом (по ТУ)</t>
+          <t>Счётчик холодной воды Ду20…25 с импульсным выходом (по ТУ посёлка)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -4002,7 +3938,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Редуктор давления Ду32 с манометром</t>
+          <t>Редуктор давления Ду32 3,5 бар с манометром</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -4032,7 +3968,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Фильтр тонкой очистки самопромывной Ду32</t>
+          <t>Фильтр тонкой очистки самопромывной Ду32, 20 мкм</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -4062,7 +3998,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Система защиты от протечек: контроллер, 3 крана с электроприводом, 12 датчиков</t>
+          <t>Установка обратного осмоса 50–100 л/ч с баком 50 л (увлажнители, питьевая вода)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -4074,10 +4010,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>90000</v>
+        <v>150000</v>
       </c>
       <c r="F6" s="4">
         <f>C6*D6</f>
@@ -4092,7 +4028,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Насосная станция повышения давления (при необходимости по замеру)</t>
+          <t>Система защиты от протечек: контроллер, 3 крана с электроприводом, 15 датчиков, датчик давления и расхода</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4107,7 +4043,7 @@
         <v>40000</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>120000</v>
+        <v>90000</v>
       </c>
       <c r="F7" s="4">
         <f>C7*D7</f>
@@ -4122,22 +4058,22 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Труба ПЭ100 SDR11 Ø32 (ввод, от фундамента до ВУ)</t>
+          <t>Насосная станция повышения давления с гидроаккумулятором 100 л</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>150</v>
+        <v>40000</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>300</v>
+        <v>120000</v>
       </c>
       <c r="F8" s="4">
         <f>C8*D8</f>
@@ -4152,7 +4088,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 25×3,5 / 32×4,4 в теплоизоляции (магистрали, стояки В1, Т3)</t>
+          <t>Труба ПЭ100 SDR11 Ø32 (ввод в котельную) с греющим кабелем</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -4161,13 +4097,13 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>140</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="F9" s="4">
         <f>C9*D9</f>
@@ -4182,7 +4118,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,2 / 20×2,8 в гофре (подводки, Т4)</t>
+          <t>Труба PE-Xa 25×3,5 / 32×4,4 в теплоизоляции (магистрали, стояки В1, Т3)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -4191,13 +4127,13 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="F10" s="4">
         <f>C10*D10</f>
@@ -4212,22 +4148,22 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Коллекторы сантехнические с кранами на 3…6 выходов</t>
+          <t>Труба PE-Xa 16×2,2 / 20×2,8 в гофре (подводки, Т4)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8</v>
+        <v>650</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6000</v>
+        <v>200</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>15000</v>
+        <v>400</v>
       </c>
       <c r="F11" s="4">
         <f>C11*D11</f>
@@ -4242,7 +4178,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Клапан балансировочный термостатический Т4 Ду15</t>
+          <t>Коллекторы сантехнические с кранами (Ст.-1, Ст.-2, Ст.-3) в шкафах</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -4251,13 +4187,13 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="F12" s="4">
         <f>C12*D12</f>
@@ -4272,22 +4208,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Труба ПП малошумная Ø110 (стояки, выпуски)</t>
+          <t>Клапан балансировочный термостатический Т4 Ду15</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>700</v>
+        <v>5000</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1300</v>
+        <v>10000</v>
       </c>
       <c r="F13" s="4">
         <f>C13*D13</f>
@@ -4302,7 +4238,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Труба ПП малошумная Ø50 (отводы)</t>
+          <t>Труба ПП малошумная Ø110 (стояки, выпуски)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -4311,13 +4247,13 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>650</v>
+        <v>1300</v>
       </c>
       <c r="F14" s="4">
         <f>C14*D14</f>
@@ -4332,22 +4268,22 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Фасонные части ПП, ревизии, хомуты с компенсацией</t>
+          <t>Труба ПП малошумная Ø50 (отводы)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>60000</v>
+        <v>350</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>120000</v>
+        <v>650</v>
       </c>
       <c r="F15" s="4">
         <f>C15*D15</f>
@@ -4362,22 +4298,22 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Противопожарные муфты Ø110</t>
+          <t>Фасонные части ПП, ревизии, хомуты с компенсацией</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1500</v>
+        <v>60000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3500</v>
+        <v>120000</v>
       </c>
       <c r="F16" s="4">
         <f>C16*D16</f>
@@ -4392,7 +4328,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Вакуумный клапан Ø110</t>
+          <t>Противопожарные муфты Ø110</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -4401,13 +4337,13 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>7000</v>
+        <v>3500</v>
       </c>
       <c r="F17" s="4">
         <f>C17*D17</f>
@@ -4422,22 +4358,22 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Проходной элемент вентиляции канализации Ø110 для фальцевой кровли</t>
+          <t>Вакуумный клапан Ø110</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="F18" s="4">
         <f>C18*D18</f>
@@ -4452,22 +4388,22 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Трап с сухим затвором Ø50/110</t>
+          <t>Проходной элемент вентиляции канализации Ø110 для фальцевой кровли</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="F19" s="4">
         <f>C19*D19</f>
@@ -4482,7 +4418,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Ванна</t>
+          <t>Трап с сухим затвором Ø50/110</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4491,13 +4427,13 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="F20" s="4">
         <f>C20*D20</f>
@@ -4507,16 +4443,12 @@
         <f>C20*E20</f>
         <v/>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>поставка заказчика</t>
-        </is>
-      </c>
+      <c r="H20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Душ</t>
+          <t>Кран поливочный незамерзающий Ø32 (ПК-1…ПК-3)</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4525,13 +4457,13 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F21" s="4">
         <f>C21*D21</f>
@@ -4541,16 +4473,12 @@
         <f>C21*E21</f>
         <v/>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>поставка заказчика</t>
-        </is>
-      </c>
+      <c r="H21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Мойка</t>
+          <t>Ванна</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4559,7 +4487,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>0</v>
@@ -4584,7 +4512,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Мойка хоз.</t>
+          <t>Душ</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4593,7 +4521,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>0</v>
@@ -4618,7 +4546,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Мойка кухонная</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4652,7 +4580,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Мойка хоз./барная</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4661,7 +4589,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>0</v>
@@ -4686,7 +4614,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Умывальник</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4695,7 +4623,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>0</v>
@@ -4720,7 +4648,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Унитаз</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4729,7 +4657,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>0</v>
@@ -4754,7 +4682,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Инсталляции для подвесных унитазов</t>
+          <t>Сушильная машина</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -4763,13 +4691,13 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="F28" s="4">
         <f>C28*D28</f>
@@ -4779,12 +4707,16 @@
         <f>C28*E28</f>
         <v/>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>поставка заказчика</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Поливочный кран морозостойкий</t>
+          <t>Умывальник</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4793,13 +4725,13 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="F29" s="4">
         <f>C29*D29</f>
@@ -4809,76 +4741,100 @@
         <f>C29*E29</f>
         <v/>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>поставка заказчика</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Материалы и оборудование (этап 1)</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
+          <t>Унитаз подвесной</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F30" s="4">
-        <f>SUMIF(H2:H29,"",F2:F29)</f>
+        <f>C30*D30</f>
         <v/>
       </c>
       <c r="G30" s="4">
-        <f>SUMIF(H2:H29,"",G2:G29)</f>
-        <v/>
-      </c>
-      <c r="H30" s="3" t="n"/>
+        <f>C30*E30</f>
+        <v/>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>поставка заказчика</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Монтажные работы</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n">
-        <v>268312</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>357750</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
+          <t>Инсталляции для подвесных унитазов</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F31" s="4">
+        <f>C31*D31</f>
+        <v/>
+      </c>
+      <c r="G31" s="4">
+        <f>C31*E31</f>
+        <v/>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Крепёж, расходники, доставка</t>
+          <t>Материалы и оборудование (этап 1)</t>
         </is>
       </c>
       <c r="B32" s="3" t="n"/>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n">
-        <v>35775</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>59625</v>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
+      <c r="F32" s="4">
+        <f>SUMIF(H2:H31,"",F2:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="4">
+        <f>SUMIF(H2:H31,"",G2:G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Установка сантехприборов заказчика (27 шт.)</t>
+          <t>Монтажные работы</t>
         </is>
       </c>
       <c r="B33" s="3" t="n"/>
@@ -4886,10 +4842,10 @@
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n">
-        <v>108000</v>
+        <v>314865</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>270000</v>
+        <v>419820</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -4900,7 +4856,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Гидравлические испытания, промывка, акты</t>
+          <t>Крепёж, расходники, доставка</t>
         </is>
       </c>
       <c r="B34" s="3" t="n"/>
@@ -4908,36 +4864,80 @@
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n">
+        <v>41982</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>69970</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Установка сантехприборов заказчика (27 шт.)</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n">
+        <v>108000</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>270000</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Гидравлические испытания, промывка, акты</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n">
         <v>20000</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>оценка</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>ИТОГО этап 1</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6">
-        <f>SUM(F30:F34)</f>
-        <v/>
-      </c>
-      <c r="G35" s="6">
-        <f>SUM(G30:G34)</f>
-        <v/>
-      </c>
-      <c r="H35" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6">
+        <f>SUM(F32:F36)</f>
+        <v/>
+      </c>
+      <c r="G37" s="6">
+        <f>SUM(G32:G36)</f>
+        <v/>
+      </c>
+      <c r="H37" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4950,7 +4950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -5008,7 +5008,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Шкаф учёта уличный с QF C80 3P и счётчиком 3ф (по ТУ)</t>
+          <t>Узел учёта 3ф с Modbus RTU (по ТУ посёлка)</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -5020,10 +5020,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>90000</v>
+        <v>70000</v>
       </c>
       <c r="F2" s="4">
         <f>C2*D2</f>
@@ -5038,7 +5038,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Щит распределительный навесной 72 мод.: QS 100 A, QF C80 3P, УЗИП I+II, реле приоритета, шины N/PE, автоматы отходящих линий</t>
+          <t>Щит ГРЩ 3 секции (О/Г/Б): QS 63 А, QF 3P 50 А, УЗИП I+II, реле напряжения ×3, ограничитель нагрузки, АВР сеть/генератор, шины N/PE, ГЗШ</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -5050,10 +5050,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>180000</v>
+        <v>250000</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="F3" s="4">
         <f>C3*D3</f>
@@ -5068,7 +5068,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Щит распределительный встраиваемый 72/48 мод. с автоматами и УЗО по схемам</t>
+          <t>Щиты этажей (секции О и Б) с АВДТ, противопожарным УЗО 300 мА, модулями DALI-2 / 0–10 В и реле освещения, резерв 30 %</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -5080,10 +5080,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>280000</v>
+        <v>450000</v>
       </c>
       <c r="F4" s="4">
         <f>C4*D4</f>
@@ -5098,7 +5098,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Щит навесной 36/24 мод. с автоматами по схемам</t>
+          <t>Щиты котельной и чердака с автоматами и АВДТ</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -5110,10 +5110,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="F5" s="4">
         <f>C5*D5</f>
@@ -5128,7 +5128,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Щит уличный IP65 12 мод., УЗО, автоматы, реле времени/фотореле</t>
+          <t>Щит уличный IP65, астротаймер, контакторы антиобледенения</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -5158,22 +5158,22 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-LS 3×1,5</t>
+          <t>Инвертор гибридный 3ф 10–12 кВт, переключение &lt; 20 мс, Modbus</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>900</v>
+        <v>1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>70</v>
+        <v>250000</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>110</v>
+        <v>450000</v>
       </c>
       <c r="F7" s="4">
         <f>C7*D7</f>
@@ -5188,22 +5188,22 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-LS 3×2,5</t>
+          <t>Аккумуляторная батарея LiFePO4 15 кВт·ч с BMS</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1100</v>
+        <v>1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>100</v>
+        <v>450000</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>160</v>
+        <v>750000</v>
       </c>
       <c r="F8" s="4">
         <f>C8*D8</f>
@@ -5218,22 +5218,22 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-LS 3×4 / 3×10</t>
+          <t>Генератор 8–10 кВт с автозапуском, шумозащитный кожух, площадка 2,5×1,5 м</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>200</v>
+        <v>300000</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>500</v>
+        <v>600000</v>
       </c>
       <c r="F9" s="4">
         <f>C9*D9</f>
@@ -5248,22 +5248,22 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-LS 5×2,5 / 5×4 / 5×6</t>
+          <t>Зарядная станция 7,4 кВт, OCPP 1.6J, динамическое ограничение тока</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>250</v>
+        <v>60000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>600</v>
+        <v>150000</v>
       </c>
       <c r="F10" s="4">
         <f>C10*D10</f>
@@ -5278,7 +5278,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-LS 5×10 / 5×16</t>
+          <t>Кабель ВВГнг(А)-LS 3×1,5 (освещение, управление)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5287,13 +5287,13 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>700</v>
-      </c>
       <c r="E11" s="4" t="n">
-        <v>1300</v>
+        <v>110</v>
       </c>
       <c r="F11" s="4">
         <f>C11*D11</f>
@@ -5308,7 +5308,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Кабель ввода АВБбШв 4×35 (или ВБбШв 5×16)</t>
+          <t>Кабель ВВГнг(А)-LS 3×2,5 (розетки)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>40</v>
+        <v>1200</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1100</v>
+        <v>160</v>
       </c>
       <c r="F12" s="4">
         <f>C12*D12</f>
@@ -5338,7 +5338,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная тонкостенная / металлорукав РЗ-ЦХ Ø16…32 с фитингами</t>
+          <t>Кабель ВВГнг(А)-LS 3×4 / 3×10</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -5347,13 +5347,13 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1600</v>
+        <v>80</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F13" s="4">
         <f>C13*D13</f>
@@ -5368,22 +5368,22 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Коробки монтажные металлические / огнестойкие</t>
+          <t>Кабель ВВГнг(А)-LS 5×2,5 / 5×4 / 5×6</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>157</v>
+        <v>260</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F14" s="4">
         <f>C14*D14</f>
@@ -5398,22 +5398,22 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Розетка 16 А с заземлением (IP20 / IP44 в С/У)</t>
+          <t>Кабель управления DALI-2 / 0–10 В 2×1,5</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>97</v>
+        <v>900</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3500</v>
+        <v>120</v>
       </c>
       <c r="F15" s="4">
         <f>C15*D15</f>
@@ -5428,22 +5428,22 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Розетка наружная IP54</t>
+          <t>Кабель ввода в земле (сечение — по ТУ, мин. 4×35 Al / 5×16 Cu)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="F16" s="4">
         <f>C16*D16</f>
@@ -5458,22 +5458,22 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Выключатель 1–2 клавиши / проходной</t>
+          <t>Кабель наружный ВБбШв 3×2,5 / 3×6 / 3×10 в ПНД</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4000</v>
+        <v>700</v>
       </c>
       <c r="F17" s="4">
         <f>C17*D17</f>
@@ -5488,22 +5488,22 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Светильник LED 15 Вт ≈ 1500 лм (тип по дизайн-проекту)</t>
+          <t>Труба стальная тонкостенная / металлорукав РЗ-ЦХ Ø16…32 с фитингами</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>107</v>
+        <v>2000</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2500</v>
+        <v>150</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>12000</v>
+        <v>400</v>
       </c>
       <c r="F18" s="4">
         <f>C18*D18</f>
@@ -5518,7 +5518,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Светильник наружный фасадный IP65</t>
+          <t>Коробки монтажные металлические, подрозетники 60 мм</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>8</v>
+        <v>260</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>4000</v>
+        <v>300</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>15000</v>
+        <v>800</v>
       </c>
       <c r="F19" s="4">
         <f>C19*D19</f>
@@ -5548,7 +5548,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Светильник для сауны +125 °C IP54</t>
+          <t>УЗИП класс III у стойки СС</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>5000</v>
@@ -5578,22 +5578,22 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Освещение и розетка чердака, светильник IP54</t>
+          <t>Розетка 16 А с заземлением (IP20 / IP44 в С/У)</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>5000</v>
+        <v>900</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>12000</v>
+        <v>1600</v>
       </c>
       <c r="F21" s="4">
         <f>C21*D21</f>
@@ -5608,108 +5608,408 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Материалы и оборудование (этап 1)</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
+          <t>Розетка с USB-C</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>3500</v>
+      </c>
       <c r="F22" s="4">
-        <f>SUMIF(H2:H21,"",F2:F21)</f>
+        <f>C22*D22</f>
         <v/>
       </c>
       <c r="G22" s="4">
-        <f>SUMIF(H2:H21,"",G2:G21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="3" t="n"/>
+        <f>C22*E22</f>
+        <v/>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Монтажные работы</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n">
-        <v>885610</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1368670</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
+          <t>Розетка наружная IP44</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F23" s="4">
+        <f>C23*D23</f>
+        <v/>
+      </c>
+      <c r="G23" s="4">
+        <f>C23*E23</f>
+        <v/>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Крепёж, расходники, доставка</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n">
-        <v>80510</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>128816</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
+          <t>Выключатель / кнопка (посты у входа и у кровати)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F24" s="4">
+        <f>C24*D24</f>
+        <v/>
+      </c>
+      <c r="G24" s="4">
+        <f>C24*E24</f>
+        <v/>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>Поворотный диммер (гостиная, мастер, спа)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F25" s="4">
+        <f>C25*D25</f>
+        <v/>
+      </c>
+      <c r="G25" s="4">
+        <f>C25*E25</f>
+        <v/>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Напольный лючок / выдвижной розеточный блок</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F26" s="4">
+        <f>C26*D26</f>
+        <v/>
+      </c>
+      <c r="G26" s="4">
+        <f>C26*E26</f>
+        <v/>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Светильник внутренний Maytoni — 69 групп (люстры, подвесы, бра, подсветка балок, споты в техпомещениях)</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="F27" s="4">
+        <f>C27*D27</f>
+        <v/>
+      </c>
+      <c r="G27" s="4">
+        <f>C27*E27</f>
+        <v/>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Светильник наружный фасадный IP65</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F28" s="4">
+        <f>C28*D28</f>
+        <v/>
+      </c>
+      <c r="G28" s="4">
+        <f>C28*E28</f>
+        <v/>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Светильник для сауны: оптоволокно, LED 24 В IP65 +125 °C</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F29" s="4">
+        <f>C29*D29</f>
+        <v/>
+      </c>
+      <c r="G29" s="4">
+        <f>C29*E29</f>
+        <v/>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Блок питания LED промышленного класса (запас ≥ 30 %), драйвер DALI-2</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F30" s="4">
+        <f>C30*D30</f>
+        <v/>
+      </c>
+      <c r="G30" s="4">
+        <f>C30*E30</f>
+        <v/>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Освещение и розетка чердака IP54</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F31" s="4">
+        <f>C31*D31</f>
+        <v/>
+      </c>
+      <c r="G31" s="4">
+        <f>C31*E31</f>
+        <v/>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Материалы и оборудование (этап 1)</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4">
+        <f>SUMIF(H2:H31,"",F2:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="4">
+        <f>SUMIF(H2:H31,"",G2:G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Монтажные работы</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n">
+        <v>1666400</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>2499600</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Крепёж, расходники, доставка</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n">
+        <v>208300</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>333280</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
           <t>Электроизмерительная лаборатория, протоколы, техотчёт</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n">
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n">
         <v>40000</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>90000</v>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>оценка</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>ИТОГО этап 1</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6">
-        <f>SUM(F22:F25)</f>
-        <v/>
-      </c>
-      <c r="G26" s="6">
-        <f>SUM(G22:G25)</f>
-        <v/>
-      </c>
-      <c r="H26" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6">
+        <f>SUM(F32:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="6">
+        <f>SUM(G32:G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5722,7 +6022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -5780,7 +6080,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Шкаф 19" 12U настенный с вентиляцией и полками</t>
+          <t>Стойка напольная 19" 18U 600×800 с вентиляцией, полками, PDU управляемый</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -5792,10 +6092,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>35000</v>
+        <v>90000</v>
       </c>
       <c r="F2" s="4">
         <f>C2*D2</f>
@@ -5810,7 +6110,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Оптический терминал провайдера (ОНТ)</t>
+          <t>Маршрутизатор с резервным LTE-каналом, VPN (Tailscale)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -5822,10 +6122,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>5000</v>
+        <v>40000</v>
       </c>
       <c r="F3" s="4">
         <f>C3*D3</f>
@@ -5840,7 +6140,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Маршрутизатор с поддержкой резервного LTE-канала</t>
+          <t>Коммутатор PoE+ 48 портов, управляемый, VLAN, бюджет ≥ 370–500 Вт</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -5852,10 +6152,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="F4" s="4">
         <f>C4*D4</f>
@@ -5870,7 +6170,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Коммутатор PoE+ 24 порта, управляемый</t>
+          <t>Сервер Home Assistant: мини-ПК Intel N100, 16 ГБ, SSD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -5882,10 +6182,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>35000</v>
+        <v>40000</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>90000</v>
+        <v>80000</v>
       </c>
       <c r="F5" s="4">
         <f>C5*D5</f>
@@ -5900,22 +6200,22 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Видеорегистратор (NVR) 16 каналов, HDD 2×4 ТБ</t>
+          <t>NAS 2 диска (архив камер 30 сут, Frigate, резервные копии HA)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="F6" s="4">
         <f>C6*D6</f>
@@ -5930,22 +6230,22 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Контроллер «умного дома» с модулями Modbus/KNX, шлюз VRF</t>
+          <t>ИБП онлайн для стойки (≥ 30 мин), NUT по USB/SNMP</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>300000</v>
+        <v>90000</v>
       </c>
       <c r="F7" s="4">
         <f>C7*D7</f>
@@ -5960,7 +6260,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>ИБП 1 кВА онлайн</t>
+          <t>Координатор Zigbee SLZB-06 с PoE (Zigbee2MQTT)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -5969,13 +6269,13 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>60000</v>
+        <v>8000</v>
       </c>
       <c r="F8" s="4">
         <f>C8*D8</f>
@@ -5990,7 +6290,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Точка доступа Wi-Fi 6/7 потолочная, PoE</t>
+          <t>Точка доступа Wi-Fi 6, PoE (потолочная / уличная на террасе)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -5999,7 +6299,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>12000</v>
@@ -6020,7 +6320,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>IP-камера 4 Мп уличная, ИК 30 м, PoE</t>
+          <t>IP-камера ONVIF Profile S/T, PoE, уличная</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -6050,7 +6350,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Вызывная панель IP с камерой, электрозамок калитки</t>
+          <t>Домофон 2N: вызывная панель с камерой (SIP/RTSP/API), монитор, замок Zigbee/Matter</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -6062,10 +6362,10 @@
         <v>1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>20000</v>
+        <v>120000</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>60000</v>
+        <v>300000</v>
       </c>
       <c r="F11" s="4">
         <f>C11*D11</f>
@@ -6080,22 +6380,22 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Монитор домофона IP 7"</t>
+          <t>Охранная система Ajax: хаб, ретрансляторы ×2, датчики открытия/движения</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>15000</v>
+        <v>80000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>40000</v>
+        <v>200000</v>
       </c>
       <c r="F12" s="4">
         <f>C12*D12</f>
@@ -6110,7 +6410,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Розетка RJ45 cat.6 двойная</t>
+          <t>Станция Алиса (кухня — с экраном, терраса — влагозащищённая)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6119,13 +6419,13 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3000</v>
+        <v>35000</v>
       </c>
       <c r="F13" s="4">
         <f>C13*D13</f>
@@ -6140,22 +6440,22 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Розетка ТВ/HDMI-over-IP</t>
+          <t>Усилитель / мультирум 6 зон с IP API, колонки потолочные</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3000</v>
+        <v>400000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>15000</v>
+        <v>1200000</v>
       </c>
       <c r="F14" s="4">
         <f>C14*D14</f>
@@ -6170,7 +6470,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Датчики открытия/движения (к централи 291-МЗ.ПС)</t>
+          <t>Динамик термостойкий для сауны (до 120 °C)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6179,13 +6479,13 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5000</v>
+        <v>40000</v>
       </c>
       <c r="F15" s="4">
         <f>C15*D15</f>
@@ -6200,22 +6500,22 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Кабель U/UTP cat.6 LSZH</t>
+          <t>Розетка RJ45 cat.6 двойная (ТВ, рабочие места, кабинет-гостевая 2 шт.)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>900</v>
+        <v>14</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>45</v>
+        <v>1000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>90</v>
+        <v>3000</v>
       </c>
       <c r="F16" s="4">
         <f>C16*D16</f>
@@ -6230,22 +6530,22 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Кабель U/UTP cat.6 наружный (в земле — в трубе)</t>
+          <t>Датчики Zigbee: температура/влажность, CO₂ (спальни, гостиная)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>70</v>
+        <v>2000</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>130</v>
+        <v>8000</v>
       </c>
       <c r="F17" s="4">
         <f>C17*D17</f>
@@ -6260,22 +6560,22 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Труба ПНД Ø50 (ввод, калитка)</t>
+          <t>Метеостанция Ecowitt (локальный API)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>80</v>
+        <v>20000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>150</v>
+        <v>40000</v>
       </c>
       <c r="F18" s="4">
         <f>C18*D18</f>
@@ -6290,7 +6590,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Металлорукав / гофра Ø20 для слаботочки</t>
+          <t>Кабель U/UTP cat.6 LSZH</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -6299,13 +6599,13 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="F19" s="4">
         <f>C19*D19</f>
@@ -6320,108 +6620,258 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Материалы и оборудование (этап 1)</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
+          <t>Кабель U/UTP cat.6 наружный (в земле — в трубе)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>130</v>
+      </c>
       <c r="F20" s="4">
-        <f>SUMIF(H2:H19,"",F2:F19)</f>
+        <f>C20*D20</f>
         <v/>
       </c>
       <c r="G20" s="4">
-        <f>SUMIF(H2:H19,"",G2:G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="3" t="n"/>
+        <f>C20*E20</f>
+        <v/>
+      </c>
+      <c r="H20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Монтажные работы</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n">
-        <v>225720</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>338580</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
+          <t>Кабель RS-485 экранированная витая пара 2×2×0,5</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="F21" s="4">
+        <f>C21*D21</f>
+        <v/>
+      </c>
+      <c r="G21" s="4">
+        <f>C21*E21</f>
+        <v/>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Крепёж, расходники, доставка</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n">
-        <v>28215</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>45144</v>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
+          <t>Кабель акустический 2×1,5 (6 зон, 5.1)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F22" s="4">
+        <f>C22*D22</f>
+        <v/>
+      </c>
+      <c r="G22" s="4">
+        <f>C22*E22</f>
+        <v/>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Труба ПНД Ø50 (оптика, калитка, ворота, зарядка ЭМ)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F23" s="4">
+        <f>C23*D23</f>
+        <v/>
+      </c>
+      <c r="G23" s="4">
+        <f>C23*E23</f>
+        <v/>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Металлорукав / гофра Ø20–25 для слаботочки, трубы Ø32 к ТВ</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F24" s="4">
+        <f>C24*D24</f>
+        <v/>
+      </c>
+      <c r="G24" s="4">
+        <f>C24*E24</f>
+        <v/>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Материалы и оборудование (этап 1)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4">
+        <f>SUMIF(H2:H24,"",F2:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="4">
+        <f>SUMIF(H2:H24,"",G2:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Монтажные работы</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n">
+        <v>552400</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>828600</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Крепёж, расходники, доставка</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n">
+        <v>69050</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>110480</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>Настройка сети, видеонаблюдения, домофона и «умного дома»</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n">
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n">
         <v>40000</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>120000</v>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>оценка</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>ИТОГО этап 1</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6">
-        <f>SUM(F20:F23)</f>
-        <v/>
-      </c>
-      <c r="G24" s="6">
-        <f>SUM(G20:G23)</f>
-        <v/>
-      </c>
-      <c r="H24" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6">
+        <f>SUM(F25:F28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="6">
+        <f>SUM(G25:G28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6434,7 +6884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -6492,22 +6942,22 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Молниеприёмник стержневой Ø16 L=1,5 м оцинк. с креплением</t>
+          <t>Пруток Ø8 оцинк. — молниеприёмная сетка по коньку, рёбрам, карнизу</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>4000</v>
+        <v>150</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>10000</v>
+        <v>300</v>
       </c>
       <c r="F2" s="4">
         <f>C2*D2</f>
@@ -6522,22 +6972,22 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Перемычки кровли (провод/полоса 16 мм²) с зажимами для фальца</t>
+          <t>Держатели прутка на фальцевую кровлю (без проколов), шаг ≤ 1 м</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>15000</v>
+        <v>300</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>35000</v>
+        <v>700</v>
       </c>
       <c r="F3" s="4">
         <f>C3*D3</f>
@@ -6552,22 +7002,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Пруток Ø8 оцинк. (токоотводы)</t>
+          <t>Молниеприёмник стержневой Ø16 L=1,0…1,5 м с креплением к дымоходу/узлу</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>150</v>
+        <v>4000</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>300</v>
+        <v>10000</v>
       </c>
       <c r="F4" s="4">
         <f>C4*D4</f>
@@ -6582,22 +7032,22 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Держатели токоотвода на фасад с отступом 100 мм</t>
+          <t>Пруток Ø8 оцинк. (токоотводы)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F5" s="4">
         <f>C5*D5</f>
@@ -6612,7 +7062,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Соединитель контрольный (разъём) токоотвод–заземлитель</t>
+          <t>Держатели токоотвода на фасад с отступом ≥ 100 мм (компенсация усадки)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -6621,13 +7071,13 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D6" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>500</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>1500</v>
       </c>
       <c r="F6" s="4">
         <f>C6*D6</f>
@@ -6642,22 +7092,22 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Полоса стальная оцинкованная 40×4</t>
+          <t>Соединитель контрольный (разъём) токоотвод–заземлитель</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="F7" s="4">
         <f>C7*D7</f>
@@ -6672,22 +7122,22 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Электрод вертикальный Ø18 L=3 м (омеднённый/оцинк.)</t>
+          <t>Полоса стальная оцинкованная 40×4 (контур, вводы, выпуски свай)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>7000</v>
+        <v>700</v>
       </c>
       <c r="F8" s="4">
         <f>C8*D8</f>
@@ -6702,7 +7152,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Главная заземляющая шина (ГЗШ)</t>
+          <t>Электрод вертикальный Ø18 L=3 м (омеднённый/оцинк.)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -6711,13 +7161,13 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="F9" s="4">
         <f>C9*D9</f>
@@ -6732,7 +7182,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Коробка ДСУП с шиной (С/У, душевые, сауна)</t>
+          <t>Выпуски 40×4 от арматуры свай З20, З21 (работы СХ)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -6741,13 +7191,13 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2500</v>
+        <v>15000</v>
       </c>
       <c r="F10" s="4">
         <f>C10*D10</f>
@@ -6762,22 +7212,22 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Провод ПуГВ 6…16 мм² жёлто-зелёный</t>
+          <t>Главная заземляющая шина (ГЗШ) в ГРЩ</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>80</v>
+        <v>3000</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>250</v>
+        <v>8000</v>
       </c>
       <c r="F11" s="4">
         <f>C11*D11</f>
@@ -6792,7 +7242,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>УЗИП класс I+II (ввод), класс II (щиты ПВУ, котельной)</t>
+          <t>Коробка ДСУП с шиной (мокрые зоны, сауна)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -6801,13 +7251,13 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>25000</v>
+        <v>2500</v>
       </c>
       <c r="F12" s="4">
         <f>C12*D12</f>
@@ -6822,22 +7272,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Измерение сопротивления заземлителя, протокол</t>
+          <t>Провод ПуГВ 6…16 мм² жёлто-зелёный</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>усл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>10000</v>
+        <v>80</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>25000</v>
+        <v>250</v>
       </c>
       <c r="F13" s="4">
         <f>C13*D13</f>
@@ -6852,22 +7302,22 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Централь (хаб) с GSM/Wi-Fi/Ethernet, релейный выход</t>
+          <t>Измерение сопротивления заземлителя, протокол</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>усл.</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="F14" s="4">
         <f>C14*D14</f>
@@ -6882,7 +7332,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Модуль реле для отключения П1В1 и П2</t>
+          <t>Централь (хаб) Ethernet/GSM, резерв питания, интеграция SIA DC-09 → HA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6891,13 +7341,13 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4000</v>
+        <v>15000</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F15" s="4">
         <f>C15*D15</f>
@@ -6912,7 +7362,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Извещатель дымовой радиоканальный</t>
+          <t>Ретранслятор радиосигнала</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -6921,13 +7371,13 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="F16" s="4">
         <f>C16*D16</f>
@@ -6942,7 +7392,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Извещатель тепловой радиоканальный</t>
+          <t>Модуль реле: отключение П1В1, П2, увлажнителей</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -6972,7 +7422,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Датчик угарного газа радиоканальный</t>
+          <t>Извещатель дымовой радиоканальный</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -6981,13 +7431,13 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>15000</v>
+        <v>9000</v>
       </c>
       <c r="F18" s="4">
         <f>C18*D18</f>
@@ -7002,7 +7452,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Оповещатель звуковой (сирена) радиоканальный</t>
+          <t>Извещатель тепловой радиоканальный (кухня, котельная, камин)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7011,13 +7461,13 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="F19" s="4">
         <f>C19*D19</f>
@@ -7032,22 +7482,22 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Датчик метана с клапаном-отсекателем (этап 2, газ)</t>
+          <t>Датчик угарного газа радиоканальный</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>15000</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>35000</v>
       </c>
       <c r="F20" s="4">
         <f>C20*D20</f>
@@ -7057,80 +7507,96 @@
         <f>C20*E20</f>
         <v/>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>этап 2</t>
-        </is>
-      </c>
+      <c r="H20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Материалы и оборудование (этап 1)</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
+          <t>Оповещатель звуковой (сирена) радиоканальный</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>12000</v>
+      </c>
       <c r="F21" s="4">
-        <f>SUMIF(H2:H20,"",F2:F20)</f>
+        <f>C21*D21</f>
         <v/>
       </c>
       <c r="G21" s="4">
-        <f>SUMIF(H2:H20,"",G2:G20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="3" t="n"/>
+        <f>C21*E21</f>
+        <v/>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Монтажные работы</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n">
-        <v>167250</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>243000</v>
+          <t>Датчики метана (котельная, кухня) с клапаном-отсекателем</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F22" s="4">
+        <f>C22*D22</f>
+        <v/>
+      </c>
+      <c r="G22" s="4">
+        <f>C22*E22</f>
+        <v/>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>оценка</t>
+          <t>этап 2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Крепёж, расходники, доставка</t>
+          <t>Материалы и оборудование (этап 1)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n"/>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n">
-        <v>16100</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>25760</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>оценка</t>
-        </is>
-      </c>
+      <c r="F23" s="4">
+        <f>SUMIF(H2:H22,"",F2:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="4">
+        <f>SUMIF(H2:H22,"",G2:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Программирование централи, проверка срабатывания ПС</t>
+          <t>Монтажные работы</t>
         </is>
       </c>
       <c r="B24" s="3" t="n"/>
@@ -7138,36 +7604,80 @@
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n">
+        <v>205330</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>296860</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Крепёж, расходники, доставка</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n">
+        <v>19130</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>30608</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Программирование централи, проверка срабатывания ПС</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>30000</v>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>оценка</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>ИТОГО этап 1</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6">
-        <f>SUM(F21:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="6">
-        <f>SUM(G21:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6">
+        <f>SUM(F23:F26)</f>
+        <v/>
+      </c>
+      <c r="G27" s="6">
+        <f>SUM(G23:G26)</f>
+        <v/>
+      </c>
+      <c r="H27" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7328,7 +7838,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Врезка в центральную сеть, водомерный колодец (по ТУ водоканала)</t>
+          <t>Врезка в посёлковую сеть, водомерный колодец (по ТУ управляющего посёлком)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7388,7 +7898,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Технологическое присоединение 50 кВт (плата по договору с Россетями)</t>
+          <t>Подключение к посёлковой ТП, 30 кВт (условия и плата — по ТУ управляющего)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7400,10 +7910,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>600000</v>
+        <v>400000</v>
       </c>
       <c r="F7" s="4">
         <f>C7*D7</f>
@@ -7478,7 +7988,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Газ (этап 2): газопровод по участку ≈ 15 м, проект ГСВ, пуск</t>
+          <t>Газ (этап 2): газопровод по участку ≈ 15 м, проект ГСВ, конденсационный котёл 35–45 кВт с монтажом, пуск</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7490,10 +8000,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>200000</v>
+        <v>450000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>550000</v>
+        <v>1100000</v>
       </c>
       <c r="F10" s="4">
         <f>C10*D10</f>
